--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.11暗号化・ハッシュ化.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.11暗号化・ハッシュ化.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E870D212-D1DE-4040-86CB-591E743FA2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F74A9B-2ECA-466E-93E9-94C2BC132344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.11.暗号化・ハッシュ化" sheetId="16" r:id="rId1"/>
@@ -457,10 +457,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/examples/01/0101_PBKDF2PasswordEncryptor.html</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>PBKDF2の実装方法については、下記Nablarchが提供する実装サンプルをベースに設計する。</t>
     <rPh sb="7" eb="9">
       <t>ジッソウ</t>
@@ -525,6 +521,10 @@
     <rPh sb="2" eb="3">
       <t>ギャク</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/biz_samples/01/0101_PBKDF2PasswordEncryptor.html</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -535,7 +535,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -586,6 +586,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -835,7 +844,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -904,7 +913,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -929,7 +938,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="0.0.A案-Template"/>
@@ -1351,12 +1360,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI37"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="17"/>
+    <col min="1" max="16384" width="3.6328125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1410,7 @@
       <c r="AH1" s="27"/>
       <c r="AI1" s="28"/>
     </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1446,7 +1455,7 @@
       <c r="AH2" s="27"/>
       <c r="AI2" s="28"/>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1487,8 +1496,8 @@
       <c r="AH3" s="27"/>
       <c r="AI3" s="28"/>
     </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
         <v>10</v>
       </c>
@@ -1496,7 +1505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="18" t="str">
         <f>$B$5&amp;"11."</f>
         <v>7.11.</v>
@@ -1505,7 +1514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D7" s="18" t="str">
         <f>$C$6&amp;"1."</f>
         <v>7.11.1.</v>
@@ -1514,7 +1523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="18"/>
       <c r="E8" s="18" t="str">
         <f>$D$7&amp;"1."</f>
@@ -1525,33 +1534,33 @@
         <v>暗号化機能概要</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F9" s="17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F10" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F11" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F12" s="17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F13" s="17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E15" s="18" t="str">
         <f>$D$7&amp;"2."</f>
         <v>7.11.1.2.</v>
@@ -1561,12 +1570,12 @@
         <v>暗号化方式</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F16" s="17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F17" s="14" t="s">
         <v>13</v>
       </c>
@@ -1605,7 +1614,7 @@
       <c r="AG17" s="15"/>
       <c r="AH17" s="16"/>
     </row>
-    <row r="18" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F18" s="19" t="s">
         <v>20</v>
       </c>
@@ -1644,7 +1653,7 @@
       <c r="AG18" s="20"/>
       <c r="AH18" s="21"/>
     </row>
-    <row r="19" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F19" s="19" t="s">
         <v>23</v>
       </c>
@@ -1683,7 +1692,7 @@
       <c r="AG19" s="20"/>
       <c r="AH19" s="21"/>
     </row>
-    <row r="20" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F20" s="19" t="s">
         <v>25</v>
       </c>
@@ -1722,14 +1731,14 @@
       <c r="AG20" s="20"/>
       <c r="AH20" s="21"/>
     </row>
-    <row r="21" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F21" s="22" t="s">
         <v>34</v>
       </c>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
-      <c r="J21" s="48" t="s">
+      <c r="J21" s="25" t="s">
         <v>39</v>
       </c>
       <c r="K21" s="23"/>
@@ -1742,7 +1751,7 @@
       <c r="R21" s="23"/>
       <c r="S21" s="23"/>
       <c r="T21" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U21" s="23"/>
       <c r="V21" s="23"/>
@@ -1761,12 +1770,12 @@
       <c r="AG21" s="23"/>
       <c r="AH21" s="24"/>
     </row>
-    <row r="22" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F22" s="17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18" t="str">
         <f>$C$6&amp;"2."</f>
         <v>7.11.2.</v>
@@ -1775,7 +1784,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E25" s="18" t="str">
         <f>$D$24&amp;"1."</f>
         <v>7.11.2.1.</v>
@@ -1785,19 +1794,19 @@
         <v>項目暗号化概要</v>
       </c>
     </row>
-    <row r="26" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E26" s="18"/>
       <c r="F26" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E27" s="18"/>
       <c r="F27" s="17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E29" s="18" t="str">
         <f>$D$24&amp;"2."</f>
         <v>7.11.2.2.</v>
@@ -1807,43 +1816,43 @@
         <v>項目暗号化方式</v>
       </c>
     </row>
-    <row r="30" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="18"/>
       <c r="F30" s="17" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="18"/>
       <c r="F31" s="17" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="18"/>
     </row>
-    <row r="33" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E33" s="18"/>
       <c r="F33" s="17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E34" s="18"/>
       <c r="F34" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E35" s="18"/>
     </row>
-    <row r="36" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E36" s="18"/>
-      <c r="F36" s="25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F36" s="48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E37" s="18"/>
     </row>
   </sheetData>

--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.11暗号化・ハッシュ化.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.11暗号化・ハッシュ化.xlsx
@@ -1,30 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F74A9B-2ECA-466E-93E9-94C2BC132344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197E10FB-5212-4093-A64C-5A7E03E67E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.11.暗号化・ハッシュ化" sheetId="16" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="_Ref390955609" localSheetId="0">'7.11.暗号化・ハッシュ化'!#REF!</definedName>
-    <definedName name="HASH" localSheetId="0">'7.11.暗号化・ハッシュ化'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'7.11.暗号化・ハッシュ化'!$A$1:$AI$38</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'7.11.暗号化・ハッシュ化'!$A$1:$AI$22</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'7.11.暗号化・ハッシュ化'!$A$1:$AI$22</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'7.11.暗号化・ハッシュ化'!$A$1:$AI$22</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'7.11.暗号化・ハッシュ化'!$A$1:$AI$22</definedName>
-    <definedName name="ハッシュアルゴリズム">'7.11.暗号化・ハッシュ化'!#REF!</definedName>
-    <definedName name="使用可能文字コード一覧">'[1]7.2.文字コード'!$AM$1:$AM$20</definedName>
-    <definedName name="通信用プロトコル">'7.11.暗号化・ハッシュ化'!#REF!</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -847,6 +832,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -912,9 +900,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -935,74 +920,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="0.0.A案-Template"/>
-      <sheetName val="0.0.A案-Sample"/>
-      <sheetName val="0.0.B案-Template"/>
-      <sheetName val="0.0.B案-Sample"/>
-      <sheetName val="0.0.A案-Sample (2)"/>
-      <sheetName val="FFG"/>
-      <sheetName val="0.0.B案-Template (2)入れ子も"/>
-      <sheetName val="7.2.文字コード"/>
-      <sheetName val="別紙・使用可能文字種一覧"/>
-      <sheetName val="⇒ＢＫ"/>
-      <sheetName val="7.2.文字コード (4)"/>
-      <sheetName val="7.2.文字コード (3)"/>
-      <sheetName val="7.2.文字コード (2)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
-        <row r="1">
-          <cell r="AM1" t="str">
-            <v>EBCDIC</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="AM2" t="str">
-            <v>MS932</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="AM3" t="str">
-            <v>Shift-JIS</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="AM4" t="str">
-            <v>UTF-8</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="AM5" t="str">
-            <v>x-windows-iso2022jp</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="AM6" t="str">
-            <v>EBCDICコード（IBM930）＋外字コード</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1356,148 +1273,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI37"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="3.6328125" style="17"/>
+    <col min="1" max="16384" width="3.625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="31"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="32"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="35"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="27"/>
-      <c r="AI1" s="28"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="29"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="40"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="41"/>
       <c r="P2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="41" t="s">
+      <c r="R2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="44"/>
       <c r="Y2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="37"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="28"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="29"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="46"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="47"/>
       <c r="Y3" s="11" t="s">
         <v>7</v>
       </c>
       <c r="Z3" s="13"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="36"/>
-      <c r="AE3" s="37"/>
-      <c r="AF3" s="26"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="28"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="29"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="18" t="s">
         <v>10</v>
       </c>
@@ -1505,7 +1422,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="18" t="str">
         <f>$B$5&amp;"11."</f>
         <v>7.11.</v>
@@ -1514,7 +1431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D7" s="18" t="str">
         <f>$C$6&amp;"1."</f>
         <v>7.11.1.</v>
@@ -1523,7 +1440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D8" s="18"/>
       <c r="E8" s="18" t="str">
         <f>$D$7&amp;"1."</f>
@@ -1534,33 +1451,33 @@
         <v>暗号化機能概要</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F9" s="17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F10" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F11" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F12" s="17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E15" s="18" t="str">
         <f>$D$7&amp;"2."</f>
         <v>7.11.1.2.</v>
@@ -1570,12 +1487,12 @@
         <v>暗号化方式</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F16" s="17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F17" s="14" t="s">
         <v>13</v>
       </c>
@@ -1614,7 +1531,7 @@
       <c r="AG17" s="15"/>
       <c r="AH17" s="16"/>
     </row>
-    <row r="18" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F18" s="19" t="s">
         <v>20</v>
       </c>
@@ -1653,7 +1570,7 @@
       <c r="AG18" s="20"/>
       <c r="AH18" s="21"/>
     </row>
-    <row r="19" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F19" s="19" t="s">
         <v>23</v>
       </c>
@@ -1692,7 +1609,7 @@
       <c r="AG19" s="20"/>
       <c r="AH19" s="21"/>
     </row>
-    <row r="20" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F20" s="19" t="s">
         <v>25</v>
       </c>
@@ -1731,7 +1648,7 @@
       <c r="AG20" s="20"/>
       <c r="AH20" s="21"/>
     </row>
-    <row r="21" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F21" s="22" t="s">
         <v>34</v>
       </c>
@@ -1770,12 +1687,12 @@
       <c r="AG21" s="23"/>
       <c r="AH21" s="24"/>
     </row>
-    <row r="22" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F22" s="17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D24" s="18" t="str">
         <f>$C$6&amp;"2."</f>
         <v>7.11.2.</v>
@@ -1784,7 +1701,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E25" s="18" t="str">
         <f>$D$24&amp;"1."</f>
         <v>7.11.2.1.</v>
@@ -1794,19 +1711,19 @@
         <v>項目暗号化概要</v>
       </c>
     </row>
-    <row r="26" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E26" s="18"/>
       <c r="F26" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E27" s="18"/>
       <c r="F27" s="17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E29" s="18" t="str">
         <f>$D$24&amp;"2."</f>
         <v>7.11.2.2.</v>
@@ -1816,43 +1733,43 @@
         <v>項目暗号化方式</v>
       </c>
     </row>
-    <row r="30" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E30" s="18"/>
       <c r="F30" s="17" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E31" s="18"/>
       <c r="F31" s="17" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="4:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E32" s="18"/>
     </row>
-    <row r="33" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E33" s="18"/>
       <c r="F33" s="17" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E34" s="18"/>
       <c r="F34" s="17" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E35" s="18"/>
     </row>
-    <row r="36" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E36" s="18"/>
-      <c r="F36" s="48" t="s">
+      <c r="F36" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="5:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E37" s="18"/>
     </row>
   </sheetData>
